--- a/artfynd/A 3412-2024 artfynd.xlsx
+++ b/artfynd/A 3412-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3412-2024 artfynd.xlsx
+++ b/artfynd/A 3412-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -795,6 +795,242 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>114956608</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56450</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Göpeknatten (Göpeknatten), Dls</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>340425</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6571405</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Vårvik</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-03-02</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>07:25</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-03-02</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>07:25</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>114956992</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56450</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Göpeknatten (Göpeknatten), Dls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>340415</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6571424</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vårvik</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-03-02</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-03-02</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3412-2024 artfynd.xlsx
+++ b/artfynd/A 3412-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1032,6 +1032,346 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121391531</v>
+      </c>
+      <c r="B5" t="n">
+        <v>90652</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Göpeknatten, Göpeknatten, Dls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>340493</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6571425</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vårvik</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121391481</v>
+      </c>
+      <c r="B6" t="n">
+        <v>90687</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Göpeknatten, Göpeknatten, Dls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>340485</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6571417</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vårvik</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121391166</v>
+      </c>
+      <c r="B7" t="n">
+        <v>94844</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Göpeknatten, Göpeknatten, Dls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>340507</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6571425</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vårvik</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>08:59</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>08:59</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3412-2024 artfynd.xlsx
+++ b/artfynd/A 3412-2024 artfynd.xlsx
@@ -1034,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121391531</v>
+        <v>121391481</v>
       </c>
       <c r="B5" t="n">
-        <v>90652</v>
+        <v>90697</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,41 +1046,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Göpeknatten, Göpeknatten, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>340493</v>
+        <v>340485</v>
       </c>
       <c r="R5" t="n">
-        <v>6571425</v>
+        <v>6571417</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1112,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1122,7 +1119,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,7 +1128,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1150,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121391481</v>
+        <v>121391166</v>
       </c>
       <c r="B6" t="n">
-        <v>90687</v>
+        <v>94854</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,25 +1158,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1190,10 +1186,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>340485</v>
+        <v>340507</v>
       </c>
       <c r="R6" t="n">
-        <v>6571417</v>
+        <v>6571425</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1235,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121391166</v>
+        <v>121391531</v>
       </c>
       <c r="B7" t="n">
-        <v>94844</v>
+        <v>90662</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,31 +1274,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Göpeknatten, Göpeknatten, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>340507</v>
+        <v>340493</v>
       </c>
       <c r="R7" t="n">
         <v>6571425</v>
@@ -1337,7 +1336,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1347,7 +1346,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,6 +1355,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 3412-2024 artfynd.xlsx
+++ b/artfynd/A 3412-2024 artfynd.xlsx
@@ -1034,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121391481</v>
+        <v>121391531</v>
       </c>
       <c r="B5" t="n">
-        <v>90697</v>
+        <v>90662</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,38 +1046,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Göpeknatten, Göpeknatten, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>340485</v>
+        <v>340493</v>
       </c>
       <c r="R5" t="n">
-        <v>6571417</v>
+        <v>6571425</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,7 +1112,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,7 +1122,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,6 +1131,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1258,10 +1262,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121391531</v>
+        <v>121391481</v>
       </c>
       <c r="B7" t="n">
-        <v>90662</v>
+        <v>90697</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,41 +1274,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Göpeknatten, Göpeknatten, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>340493</v>
+        <v>340485</v>
       </c>
       <c r="R7" t="n">
-        <v>6571425</v>
+        <v>6571417</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1336,7 +1337,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1346,7 +1347,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,7 +1356,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 3412-2024 artfynd.xlsx
+++ b/artfynd/A 3412-2024 artfynd.xlsx
@@ -1034,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121391531</v>
+        <v>121391481</v>
       </c>
       <c r="B5" t="n">
-        <v>90662</v>
+        <v>90709</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,41 +1046,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Göpeknatten, Göpeknatten, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>340493</v>
+        <v>340485</v>
       </c>
       <c r="R5" t="n">
-        <v>6571425</v>
+        <v>6571417</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1112,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1122,7 +1119,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,7 +1128,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1150,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121391166</v>
+        <v>121391531</v>
       </c>
       <c r="B6" t="n">
-        <v>94854</v>
+        <v>90674</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1166,31 +1162,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Göpeknatten, Göpeknatten, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>340507</v>
+        <v>340493</v>
       </c>
       <c r="R6" t="n">
         <v>6571425</v>
@@ -1225,7 +1224,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1235,7 +1234,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,6 +1243,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121391481</v>
+        <v>121391166</v>
       </c>
       <c r="B7" t="n">
-        <v>90697</v>
+        <v>94866</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,25 +1274,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>340485</v>
+        <v>340507</v>
       </c>
       <c r="R7" t="n">
-        <v>6571417</v>
+        <v>6571425</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 3412-2024 artfynd.xlsx
+++ b/artfynd/A 3412-2024 artfynd.xlsx
@@ -1037,7 +1037,7 @@
         <v>121391481</v>
       </c>
       <c r="B5" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>121391531</v>
       </c>
       <c r="B6" t="n">
-        <v>90674</v>
+        <v>90675</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>121391166</v>
       </c>
       <c r="B7" t="n">
-        <v>94866</v>
+        <v>94867</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 3412-2024 artfynd.xlsx
+++ b/artfynd/A 3412-2024 artfynd.xlsx
@@ -1037,7 +1037,7 @@
         <v>121391481</v>
       </c>
       <c r="B5" t="n">
-        <v>90710</v>
+        <v>90713</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1146,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121391531</v>
+        <v>121391166</v>
       </c>
       <c r="B6" t="n">
-        <v>90675</v>
+        <v>94870</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,34 +1162,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Göpeknatten, Göpeknatten, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>340493</v>
+        <v>340507</v>
       </c>
       <c r="R6" t="n">
         <v>6571425</v>
@@ -1224,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1234,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,7 +1240,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1262,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121391166</v>
+        <v>121391531</v>
       </c>
       <c r="B7" t="n">
-        <v>94867</v>
+        <v>90678</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,31 +1274,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Göpeknatten, Göpeknatten, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>340507</v>
+        <v>340493</v>
       </c>
       <c r="R7" t="n">
         <v>6571425</v>
@@ -1337,7 +1336,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1347,7 +1346,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,6 +1355,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 3412-2024 artfynd.xlsx
+++ b/artfynd/A 3412-2024 artfynd.xlsx
@@ -1146,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121391166</v>
+        <v>121391531</v>
       </c>
       <c r="B6" t="n">
-        <v>94870</v>
+        <v>90678</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,31 +1162,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Göpeknatten, Göpeknatten, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>340507</v>
+        <v>340493</v>
       </c>
       <c r="R6" t="n">
         <v>6571425</v>
@@ -1221,7 +1224,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1234,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,6 +1243,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1258,10 +1262,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121391531</v>
+        <v>121391166</v>
       </c>
       <c r="B7" t="n">
-        <v>90678</v>
+        <v>94870</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,34 +1278,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Göpeknatten, Göpeknatten, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>340493</v>
+        <v>340507</v>
       </c>
       <c r="R7" t="n">
         <v>6571425</v>
@@ -1336,7 +1337,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1346,7 +1347,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,7 +1356,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 3412-2024 artfynd.xlsx
+++ b/artfynd/A 3412-2024 artfynd.xlsx
@@ -1034,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121391481</v>
+        <v>121391166</v>
       </c>
       <c r="B5" t="n">
-        <v>90713</v>
+        <v>94876</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,25 +1046,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1074,10 +1074,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>340485</v>
+        <v>340507</v>
       </c>
       <c r="R5" t="n">
-        <v>6571417</v>
+        <v>6571425</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121391531</v>
+        <v>121391481</v>
       </c>
       <c r="B6" t="n">
-        <v>90678</v>
+        <v>90719</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,41 +1158,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Göpeknatten, Göpeknatten, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>340493</v>
+        <v>340485</v>
       </c>
       <c r="R6" t="n">
-        <v>6571425</v>
+        <v>6571417</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1234,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,7 +1240,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1262,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121391166</v>
+        <v>121391531</v>
       </c>
       <c r="B7" t="n">
-        <v>94870</v>
+        <v>90684</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,31 +1274,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Göpeknatten, Göpeknatten, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>340507</v>
+        <v>340493</v>
       </c>
       <c r="R7" t="n">
         <v>6571425</v>
@@ -1337,7 +1336,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1347,7 +1346,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,6 +1355,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 3412-2024 artfynd.xlsx
+++ b/artfynd/A 3412-2024 artfynd.xlsx
@@ -1034,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121391166</v>
+        <v>121391481</v>
       </c>
       <c r="B5" t="n">
-        <v>94876</v>
+        <v>90720</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,25 +1046,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1074,10 +1074,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>340507</v>
+        <v>340485</v>
       </c>
       <c r="R5" t="n">
-        <v>6571425</v>
+        <v>6571417</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121391481</v>
+        <v>121391166</v>
       </c>
       <c r="B6" t="n">
-        <v>90719</v>
+        <v>94877</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,25 +1158,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1186,10 +1186,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>340485</v>
+        <v>340507</v>
       </c>
       <c r="R6" t="n">
-        <v>6571417</v>
+        <v>6571425</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,7 +1261,7 @@
         <v>121391531</v>
       </c>
       <c r="B7" t="n">
-        <v>90684</v>
+        <v>90685</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 3412-2024 artfynd.xlsx
+++ b/artfynd/A 3412-2024 artfynd.xlsx
@@ -1034,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121391481</v>
+        <v>121391531</v>
       </c>
       <c r="B5" t="n">
-        <v>90720</v>
+        <v>90685</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,38 +1046,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Göpeknatten, Göpeknatten, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>340485</v>
+        <v>340493</v>
       </c>
       <c r="R5" t="n">
-        <v>6571417</v>
+        <v>6571425</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,7 +1112,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,7 +1122,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,6 +1131,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1146,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121391166</v>
+        <v>121391481</v>
       </c>
       <c r="B6" t="n">
-        <v>94877</v>
+        <v>90720</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,25 +1162,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1186,10 +1190,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>340507</v>
+        <v>340485</v>
       </c>
       <c r="R6" t="n">
-        <v>6571425</v>
+        <v>6571417</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,7 +1225,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1235,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,10 +1262,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121391531</v>
+        <v>121391166</v>
       </c>
       <c r="B7" t="n">
-        <v>90685</v>
+        <v>94877</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,34 +1278,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Göpeknatten, Göpeknatten, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>340493</v>
+        <v>340507</v>
       </c>
       <c r="R7" t="n">
         <v>6571425</v>
@@ -1336,7 +1337,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1346,7 +1347,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,7 +1356,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 3412-2024 artfynd.xlsx
+++ b/artfynd/A 3412-2024 artfynd.xlsx
@@ -1034,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121391531</v>
+        <v>121391481</v>
       </c>
       <c r="B5" t="n">
-        <v>90685</v>
+        <v>90720</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,41 +1046,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Göpeknatten, Göpeknatten, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>340493</v>
+        <v>340485</v>
       </c>
       <c r="R5" t="n">
-        <v>6571425</v>
+        <v>6571417</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1112,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1122,7 +1119,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,7 +1128,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1150,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121391481</v>
+        <v>121391166</v>
       </c>
       <c r="B6" t="n">
-        <v>90720</v>
+        <v>94877</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,25 +1158,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1190,10 +1186,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>340485</v>
+        <v>340507</v>
       </c>
       <c r="R6" t="n">
-        <v>6571417</v>
+        <v>6571425</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1235,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121391166</v>
+        <v>121391531</v>
       </c>
       <c r="B7" t="n">
-        <v>94877</v>
+        <v>90685</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,31 +1274,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Göpeknatten, Göpeknatten, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>340507</v>
+        <v>340493</v>
       </c>
       <c r="R7" t="n">
         <v>6571425</v>
@@ -1337,7 +1336,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1347,7 +1346,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,6 +1355,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 3412-2024 artfynd.xlsx
+++ b/artfynd/A 3412-2024 artfynd.xlsx
@@ -1037,7 +1037,7 @@
         <v>121391481</v>
       </c>
       <c r="B5" t="n">
-        <v>90720</v>
+        <v>90728</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1146,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121391166</v>
+        <v>121391531</v>
       </c>
       <c r="B6" t="n">
-        <v>94877</v>
+        <v>90693</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,31 +1162,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Göpeknatten, Göpeknatten, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>340507</v>
+        <v>340493</v>
       </c>
       <c r="R6" t="n">
         <v>6571425</v>
@@ -1221,7 +1224,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1234,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,6 +1243,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1258,10 +1262,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121391531</v>
+        <v>121391166</v>
       </c>
       <c r="B7" t="n">
-        <v>90685</v>
+        <v>94885</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,34 +1278,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Göpeknatten, Göpeknatten, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>340493</v>
+        <v>340507</v>
       </c>
       <c r="R7" t="n">
         <v>6571425</v>
@@ -1336,7 +1337,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1346,7 +1347,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,7 +1356,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 3412-2024 artfynd.xlsx
+++ b/artfynd/A 3412-2024 artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>114559036</v>
       </c>
       <c r="B2" t="n">
-        <v>56478</v>
+        <v>56688</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Göpeknatten (Göpeknatten), Dls</t>
+          <t>Göpeknatten, Göpeknatten, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">

--- a/artfynd/A 3412-2024 artfynd.xlsx
+++ b/artfynd/A 3412-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>114559036</v>
       </c>
       <c r="B2" t="n">
-        <v>56688</v>
+        <v>56691</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 3412-2024 artfynd.xlsx
+++ b/artfynd/A 3412-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>114559036</v>
       </c>
       <c r="B2" t="n">
-        <v>56691</v>
+        <v>56697</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 3412-2024 artfynd.xlsx
+++ b/artfynd/A 3412-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>114559036</v>
       </c>
       <c r="B2" t="n">
-        <v>56697</v>
+        <v>56700</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 3412-2024 artfynd.xlsx
+++ b/artfynd/A 3412-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,56 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114559036</v>
+        <v>121391481</v>
       </c>
       <c r="B2" t="n">
-        <v>56700</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Göpeknatten, Göpeknatten, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>340445</v>
+        <v>340485</v>
       </c>
       <c r="R2" t="n">
-        <v>6571420</v>
+        <v>6571417</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,27 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:32</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Spillning på snö</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114956992</v>
+        <v>121391166</v>
       </c>
       <c r="B3" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -814,40 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Göpeknatten (Göpeknatten), Dls</t>
+          <t>Göpeknatten, Göpeknatten, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>340415</v>
+        <v>340507</v>
       </c>
       <c r="R3" t="n">
-        <v>6571424</v>
+        <v>6571425</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,22 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114956608</v>
+        <v>121391531</v>
       </c>
       <c r="B4" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -932,40 +900,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Göpeknatten (Göpeknatten), Dls</t>
+          <t>Göpeknatten, Göpeknatten, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>340425</v>
+        <v>340493</v>
       </c>
       <c r="R4" t="n">
-        <v>6571406</v>
+        <v>6571425</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,22 +957,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>07:25</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>07:25</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,6 +981,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1034,15 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121391166</v>
+        <v>114559036</v>
       </c>
       <c r="B5" t="n">
-        <v>94885</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1050,34 +1011,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Göpeknatten, Göpeknatten, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>340507</v>
+        <v>340445</v>
       </c>
       <c r="R5" t="n">
-        <v>6571425</v>
+        <v>6571420</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,22 +1071,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Spillning på snö</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,50 +1118,51 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121391481</v>
+        <v>114956575</v>
       </c>
       <c r="B6" t="n">
-        <v>90728</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Göpeknatten, Göpeknatten, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>340485</v>
+        <v>340413</v>
       </c>
       <c r="R6" t="n">
-        <v>6571417</v>
+        <v>6571378</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,22 +1189,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,15 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121391531</v>
+        <v>114956608</v>
       </c>
       <c r="B7" t="n">
-        <v>90693</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,37 +1242,40 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Göpeknatten, Göpeknatten, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>340493</v>
+        <v>340425</v>
       </c>
       <c r="R7" t="n">
-        <v>6571425</v>
+        <v>6571406</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,22 +1302,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,7 +1326,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1371,6 +1341,119 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>114956992</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Göpeknatten, Göpeknatten, Dls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>340415</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6571424</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vårvik</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-03-02</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-03-02</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3412-2024 artfynd.xlsx
+++ b/artfynd/A 3412-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -790,6 +795,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114559036</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -903,6 +913,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114956575</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1016,6 +1031,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114956608</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1129,6 +1149,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114956992</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1236,6 +1261,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121391481</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1343,6 +1373,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121391166</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1454,8 +1489,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121391531</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>